--- a/demo-imports/tables-template.xlsx
+++ b/demo-imports/tables-template.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Import template" sheetId="1" r:id="Rc9f5aa09160b4716"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Import template" sheetId="1" r:id="Rd2f65086fd1544e9"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -260,7 +260,7 @@
         <x:v>Section A</x:v>
       </x:c>
       <x:c r="D2" t="n">
-        <x:v>10</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="E2" t="n">
         <x:v>584.9</x:v>
@@ -289,7 +289,7 @@
         <x:v>Section B</x:v>
       </x:c>
       <x:c r="D3" t="n">
-        <x:v>10</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="E3" t="n">
         <x:v>700</x:v>
@@ -318,7 +318,7 @@
         <x:v>Section C</x:v>
       </x:c>
       <x:c r="D4" t="n">
-        <x:v>10</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="E4" t="n">
         <x:v>768.5</x:v>
@@ -347,7 +347,7 @@
         <x:v>Section D</x:v>
       </x:c>
       <x:c r="D5" t="n">
-        <x:v>10</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="E5" t="n">
         <x:v>700.3</x:v>
@@ -376,7 +376,7 @@
         <x:v>Section E</x:v>
       </x:c>
       <x:c r="D6" t="n">
-        <x:v>10</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="E6" t="n">
         <x:v>587.5</x:v>
@@ -405,7 +405,7 @@
         <x:v>Section F</x:v>
       </x:c>
       <x:c r="D7" t="n">
-        <x:v>10</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="E7" t="n">
         <x:v>526.3</x:v>
@@ -434,7 +434,7 @@
         <x:v>Section A</x:v>
       </x:c>
       <x:c r="D8" t="n">
-        <x:v>10</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="E8" t="n">
         <x:v>538.2</x:v>
@@ -463,7 +463,7 @@
         <x:v>Section B</x:v>
       </x:c>
       <x:c r="D9" t="n">
-        <x:v>10</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="E9" t="n">
         <x:v>699.4</x:v>
@@ -492,7 +492,7 @@
         <x:v>Section C</x:v>
       </x:c>
       <x:c r="D10" t="n">
-        <x:v>10</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="E10" t="n">
         <x:v>817.3</x:v>
@@ -521,7 +521,7 @@
         <x:v>Section D</x:v>
       </x:c>
       <x:c r="D11" t="n">
-        <x:v>10</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="E11" t="n">
         <x:v>748.9</x:v>
@@ -550,7 +550,7 @@
         <x:v>Section E</x:v>
       </x:c>
       <x:c r="D12" t="n">
-        <x:v>10</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="E12" t="n">
         <x:v>584.3</x:v>
@@ -579,7 +579,7 @@
         <x:v>Section F</x:v>
       </x:c>
       <x:c r="D13" t="n">
-        <x:v>10</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="E13" t="n">
         <x:v>472.5</x:v>
@@ -608,7 +608,7 @@
         <x:v>Section A</x:v>
       </x:c>
       <x:c r="D14" t="n">
-        <x:v>10</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="E14" t="n">
         <x:v>583.1</x:v>
@@ -637,7 +637,7 @@
         <x:v>Section B</x:v>
       </x:c>
       <x:c r="D15" t="n">
-        <x:v>10</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="E15" t="n">
         <x:v>748.8</x:v>
@@ -666,7 +666,7 @@
         <x:v>Section C</x:v>
       </x:c>
       <x:c r="D16" t="n">
-        <x:v>10</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="E16" t="n">
         <x:v>817.3</x:v>
@@ -695,7 +695,7 @@
         <x:v>Section D</x:v>
       </x:c>
       <x:c r="D17" t="n">
-        <x:v>10</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="E17" t="n">
         <x:v>700.6</x:v>
@@ -724,7 +724,7 @@
         <x:v>Section E</x:v>
       </x:c>
       <x:c r="D18" t="n">
-        <x:v>10</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="E18" t="n">
         <x:v>539.3</x:v>
@@ -753,7 +753,7 @@
         <x:v>Section F</x:v>
       </x:c>
       <x:c r="D19" t="n">
-        <x:v>10</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="E19" t="n">
         <x:v>472.5</x:v>
@@ -782,7 +782,7 @@
         <x:v>Section A</x:v>
       </x:c>
       <x:c r="D20" t="n">
-        <x:v>10</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="E20" t="n">
         <x:v>488</x:v>
@@ -811,7 +811,7 @@
         <x:v>Section B</x:v>
       </x:c>
       <x:c r="D21" t="n">
-        <x:v>10</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="E21" t="n">
         <x:v>697.8</x:v>
@@ -840,7 +840,7 @@
         <x:v>Section C</x:v>
       </x:c>
       <x:c r="D22" t="n">
-        <x:v>10</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="E22" t="n">
         <x:v>864.3</x:v>
@@ -869,7 +869,7 @@
         <x:v>Section D</x:v>
       </x:c>
       <x:c r="D23" t="n">
-        <x:v>10</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="E23" t="n">
         <x:v>796.7</x:v>
@@ -898,7 +898,7 @@
         <x:v>Section E</x:v>
       </x:c>
       <x:c r="D24" t="n">
-        <x:v>10</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="E24" t="n">
         <x:v>585.6</x:v>
@@ -927,7 +927,7 @@
         <x:v>Section F</x:v>
       </x:c>
       <x:c r="D25" t="n">
-        <x:v>10</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="E25" t="n">
         <x:v>422.1</x:v>
@@ -956,7 +956,7 @@
         <x:v>Section A</x:v>
       </x:c>
       <x:c r="D26" t="n">
-        <x:v>10</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="E26" t="n">
         <x:v>534.5</x:v>
@@ -985,7 +985,7 @@
         <x:v>Section B</x:v>
       </x:c>
       <x:c r="D27" t="n">
-        <x:v>10</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="E27" t="n">
         <x:v>746.9</x:v>
@@ -1014,7 +1014,7 @@
         <x:v>Section C</x:v>
       </x:c>
       <x:c r="D28" t="n">
-        <x:v>10</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="E28" t="n">
         <x:v>864.3</x:v>
@@ -1043,7 +1043,7 @@
         <x:v>Section D</x:v>
       </x:c>
       <x:c r="D29" t="n">
-        <x:v>10</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="E29" t="n">
         <x:v>748.7</x:v>
@@ -1072,7 +1072,7 @@
         <x:v>Section E</x:v>
       </x:c>
       <x:c r="D30" t="n">
-        <x:v>10</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="E30" t="n">
         <x:v>534.8</x:v>
@@ -1101,7 +1101,7 @@
         <x:v>Section F</x:v>
       </x:c>
       <x:c r="D31" t="n">
-        <x:v>10</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="E31" t="n">
         <x:v>422.1</x:v>
@@ -1130,7 +1130,7 @@
         <x:v>Section A</x:v>
       </x:c>
       <x:c r="D32" t="n">
-        <x:v>10</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="E32" t="n">
         <x:v>582.7</x:v>
@@ -1159,7 +1159,7 @@
         <x:v>Section B</x:v>
       </x:c>
       <x:c r="D33" t="n">
-        <x:v>10</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="E33" t="n">
         <x:v>796.4</x:v>
@@ -1188,7 +1188,7 @@
         <x:v>Section C</x:v>
       </x:c>
       <x:c r="D34" t="n">
-        <x:v>10</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="E34" t="n">
         <x:v>864.3</x:v>
@@ -1217,7 +1217,7 @@
         <x:v>Section D</x:v>
       </x:c>
       <x:c r="D35" t="n">
-        <x:v>10</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="E35" t="n">
         <x:v>700.3</x:v>
@@ -1246,7 +1246,7 @@
         <x:v>Section E</x:v>
       </x:c>
       <x:c r="D36" t="n">
-        <x:v>10</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="E36" t="n">
         <x:v>488.1</x:v>
@@ -1275,7 +1275,7 @@
         <x:v>Section F</x:v>
       </x:c>
       <x:c r="D37" t="n">
-        <x:v>10</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="E37" t="n">
         <x:v>422.1</x:v>
@@ -1304,7 +1304,7 @@
         <x:v>Section A</x:v>
       </x:c>
       <x:c r="D38" t="n">
-        <x:v>10</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="E38" t="n">
         <x:v>441.6</x:v>
@@ -1333,7 +1333,7 @@
         <x:v>Section B</x:v>
       </x:c>
       <x:c r="D39" t="n">
-        <x:v>10</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="E39" t="n">
         <x:v>694.9</x:v>
@@ -1362,7 +1362,7 @@
         <x:v>Section C</x:v>
       </x:c>
       <x:c r="D40" t="n">
-        <x:v>10</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="E40" t="n">
         <x:v>911.3</x:v>
@@ -1391,7 +1391,7 @@
         <x:v>Section D</x:v>
       </x:c>
       <x:c r="D41" t="n">
-        <x:v>10</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="E41" t="n">
         <x:v>845.7</x:v>
@@ -1420,7 +1420,7 @@
         <x:v>Section E</x:v>
       </x:c>
       <x:c r="D42" t="n">
-        <x:v>10</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="E42" t="n">
         <x:v>583.1</x:v>
@@ -1449,7 +1449,7 @@
         <x:v>Section F</x:v>
       </x:c>
       <x:c r="D43" t="n">
-        <x:v>10</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="E43" t="n">
         <x:v>376.8</x:v>
@@ -1478,7 +1478,7 @@
         <x:v>Section A</x:v>
       </x:c>
       <x:c r="D44" t="n">
-        <x:v>10</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="E44" t="n">
         <x:v>484.5</x:v>
@@ -1507,7 +1507,7 @@
         <x:v>Section B</x:v>
       </x:c>
       <x:c r="D45" t="n">
-        <x:v>10</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="E45" t="n">
         <x:v>745.4</x:v>
@@ -1536,7 +1536,7 @@
         <x:v>Section C</x:v>
       </x:c>
       <x:c r="D46" t="n">
-        <x:v>10</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="E46" t="n">
         <x:v>911.3</x:v>
@@ -1565,7 +1565,7 @@
         <x:v>Section D</x:v>
       </x:c>
       <x:c r="D47" t="n">
-        <x:v>10</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="E47" t="n">
         <x:v>796.4</x:v>
@@ -1594,7 +1594,7 @@
         <x:v>Section E</x:v>
       </x:c>
       <x:c r="D48" t="n">
-        <x:v>10</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="E48" t="n">
         <x:v>536.9</x:v>
@@ -1623,7 +1623,7 @@
         <x:v>Section F</x:v>
       </x:c>
       <x:c r="D49" t="n">
-        <x:v>10</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="E49" t="n">
         <x:v>377.5</x:v>
@@ -1652,7 +1652,7 @@
         <x:v>Section A</x:v>
       </x:c>
       <x:c r="D50" t="n">
-        <x:v>10</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="E50" t="n">
         <x:v>536.3</x:v>
@@ -1681,7 +1681,7 @@
         <x:v>Section B</x:v>
       </x:c>
       <x:c r="D51" t="n">
-        <x:v>10</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="E51" t="n">
         <x:v>794.8</x:v>
@@ -1710,7 +1710,7 @@
         <x:v>Section C</x:v>
       </x:c>
       <x:c r="D52" t="n">
-        <x:v>10</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="E52" t="n">
         <x:v>911.3</x:v>
@@ -1739,7 +1739,7 @@
         <x:v>Section D</x:v>
       </x:c>
       <x:c r="D53" t="n">
-        <x:v>10</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="E53" t="n">
         <x:v>748.1</x:v>
@@ -1768,7 +1768,7 @@
         <x:v>Section E</x:v>
       </x:c>
       <x:c r="D54" t="n">
-        <x:v>10</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="E54" t="n">
         <x:v>487.1</x:v>
@@ -1797,7 +1797,7 @@
         <x:v>Section F</x:v>
       </x:c>
       <x:c r="D55" t="n">
-        <x:v>10</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="E55" t="n">
         <x:v>376.8</x:v>
@@ -1826,7 +1826,7 @@
         <x:v>Section A</x:v>
       </x:c>
       <x:c r="D56" t="n">
-        <x:v>10</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="E56" t="n">
         <x:v>584.6</x:v>
@@ -1855,7 +1855,7 @@
         <x:v>Section B</x:v>
       </x:c>
       <x:c r="D57" t="n">
-        <x:v>10</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="E57" t="n">
         <x:v>844.2</x:v>
@@ -1884,7 +1884,7 @@
         <x:v>Section C</x:v>
       </x:c>
       <x:c r="D58" t="n">
-        <x:v>10</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="E58" t="n">
         <x:v>911.3</x:v>
@@ -1913,7 +1913,7 @@
         <x:v>Section D</x:v>
       </x:c>
       <x:c r="D59" t="n">
-        <x:v>10</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="E59" t="n">
         <x:v>699.7</x:v>
@@ -1942,7 +1942,7 @@
         <x:v>Section E</x:v>
       </x:c>
       <x:c r="D60" t="n">
-        <x:v>10</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="E60" t="n">
         <x:v>437</x:v>
@@ -1971,7 +1971,7 @@
         <x:v>Section F</x:v>
       </x:c>
       <x:c r="D61" t="n">
-        <x:v>10</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="E61" t="n">
         <x:v>376.8</x:v>
@@ -2000,7 +2000,7 @@
         <x:v>Section A</x:v>
       </x:c>
       <x:c r="D62" t="n">
-        <x:v>10</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="E62" t="n">
         <x:v>442.1</x:v>
@@ -2029,7 +2029,7 @@
         <x:v>Section B</x:v>
       </x:c>
       <x:c r="D63" t="n">
-        <x:v>10</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="E63" t="n">
         <x:v>744.1</x:v>
@@ -2058,7 +2058,7 @@
         <x:v>Section C</x:v>
       </x:c>
       <x:c r="D64" t="n">
-        <x:v>10</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="E64" t="n">
         <x:v>959.1</x:v>
@@ -2087,7 +2087,7 @@
         <x:v>Section D</x:v>
       </x:c>
       <x:c r="D65" t="n">
-        <x:v>10</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="E65" t="n">
         <x:v>894.2</x:v>
@@ -2116,7 +2116,7 @@
         <x:v>Section E</x:v>
       </x:c>
       <x:c r="D66" t="n">
-        <x:v>10</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="E66" t="n">
         <x:v>535.8</x:v>
@@ -2145,7 +2145,7 @@
         <x:v>Section F</x:v>
       </x:c>
       <x:c r="D67" t="n">
-        <x:v>10</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="E67" t="n">
         <x:v>328.3</x:v>
@@ -2174,7 +2174,7 @@
         <x:v>Section A</x:v>
       </x:c>
       <x:c r="D68" t="n">
-        <x:v>10</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="E68" t="n">
         <x:v>485.9</x:v>
@@ -2203,7 +2203,7 @@
         <x:v>Section B</x:v>
       </x:c>
       <x:c r="D69" t="n">
-        <x:v>10</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="E69" t="n">
         <x:v>793.3</x:v>
@@ -2232,7 +2232,7 @@
         <x:v>Section C</x:v>
       </x:c>
       <x:c r="D70" t="n">
-        <x:v>10</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="E70" t="n">
         <x:v>961</x:v>
@@ -2261,7 +2261,7 @@
         <x:v>Section D</x:v>
       </x:c>
       <x:c r="D71" t="n">
-        <x:v>10</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="E71" t="n">
         <x:v>844.6</x:v>
@@ -2290,7 +2290,7 @@
         <x:v>Section E</x:v>
       </x:c>
       <x:c r="D72" t="n">
-        <x:v>10</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="E72" t="n">
         <x:v>484.3</x:v>
@@ -2319,7 +2319,7 @@
         <x:v>Section F</x:v>
       </x:c>
       <x:c r="D73" t="n">
-        <x:v>10</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="E73" t="n">
         <x:v>332.3</x:v>
@@ -2348,7 +2348,7 @@
         <x:v>Section A</x:v>
       </x:c>
       <x:c r="D74" t="n">
-        <x:v>10</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="E74" t="n">
         <x:v>529.5</x:v>
@@ -2377,7 +2377,7 @@
         <x:v>Section B</x:v>
       </x:c>
       <x:c r="D75" t="n">
-        <x:v>10</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="E75" t="n">
         <x:v>843.7</x:v>
@@ -2406,7 +2406,7 @@
         <x:v>Section C</x:v>
       </x:c>
       <x:c r="D76" t="n">
-        <x:v>10</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="E76" t="n">
         <x:v>961</x:v>
@@ -2435,7 +2435,7 @@
         <x:v>Section D</x:v>
       </x:c>
       <x:c r="D77" t="n">
-        <x:v>10</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="E77" t="n">
         <x:v>798.4</x:v>
@@ -2464,7 +2464,7 @@
         <x:v>Section E</x:v>
       </x:c>
       <x:c r="D78" t="n">
-        <x:v>10</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="E78" t="n">
         <x:v>436.1</x:v>
@@ -2493,7 +2493,7 @@
         <x:v>Section F</x:v>
       </x:c>
       <x:c r="D79" t="n">
-        <x:v>10</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="E79" t="n">
         <x:v>329.3</x:v>
@@ -2522,7 +2522,7 @@
         <x:v>Section C</x:v>
       </x:c>
       <x:c r="D80" t="n">
-        <x:v>10</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="E80" t="n">
         <x:v>961</x:v>
@@ -2551,7 +2551,7 @@
         <x:v>Section D</x:v>
       </x:c>
       <x:c r="D81" t="n">
-        <x:v>10</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="E81" t="n">
         <x:v>749.2</x:v>
@@ -2580,7 +2580,7 @@
         <x:v>Section E</x:v>
       </x:c>
       <x:c r="D82" t="n">
-        <x:v>10</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="E82" t="n">
         <x:v>390.5</x:v>
@@ -2609,7 +2609,7 @@
         <x:v>Section F</x:v>
       </x:c>
       <x:c r="D83" t="n">
-        <x:v>10</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="E83" t="n">
         <x:v>329.3</x:v>
@@ -2638,7 +2638,7 @@
         <x:v>Section F</x:v>
       </x:c>
       <x:c r="D84" t="n">
-        <x:v>10</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="E84" t="n">
         <x:v>329.3</x:v>
